--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6539-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6539-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4EA33CB-D257-4BCB-AFC4-244611C6BF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D63ADCB-5E6A-4BC8-877B-4CC2CAF81F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{D2FBB6F4-C525-4723-8046-899AD69E2BEF}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{E7F80658-6CD0-47FA-8C05-1574F531DF39}"/>
   </bookViews>
   <sheets>
     <sheet name="6539-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1517,25 +1517,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A6D478-CD87-4064-BF33-44FF35623CAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C2EF3C9-AA2C-4480-BECF-E29BCDA832B5}">
   <dimension ref="A1:R28"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" customWidth="1"/>
-    <col min="6" max="7" width="7.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" customWidth="1"/>
-    <col min="9" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
+    <col min="5" max="5" width="9.25" customWidth="1"/>
+    <col min="6" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="9.25" customWidth="1"/>
+    <col min="9" max="10" width="9.75" customWidth="1"/>
+    <col min="11" max="13" width="9.25" customWidth="1"/>
+    <col min="14" max="14" width="9.75" customWidth="1"/>
+    <col min="15" max="17" width="9.25" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1563,7 +1563,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1593,7 +1593,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1689,7 +1689,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="41">
         <v>2025</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="43" t="s">
         <v>26</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
       <c r="B10" s="22" t="s">
         <v>29</v>
@@ -1987,7 +1987,7 @@
       <c r="Q10" s="48"/>
       <c r="R10" s="48"/>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="39">
         <v>2024</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="41">
         <v>2023</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>7.61</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="39">
         <v>2022</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="41">
         <v>2021</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>6.01</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2020</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="41">
         <v>2019</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2018</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="41">
         <v>2017</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2016</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>2.23</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="41" t="s">
         <v>45</v>
       </c>
